--- a/output/pdf_financials_xlsx/WM.xlsx
+++ b/output/pdf_financials_xlsx/WM.xlsx
@@ -855,10 +855,10 @@
         <v>0.8732839999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.193686</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.421009</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -914,10 +914,10 @@
         <v>2.442751</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.193686</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.421009</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.27292</v>
+        <v>16.079234</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>26.023749</v>
+        <v>25.60274</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.237471</v>
@@ -1326,25 +1326,25 @@
         <v>0.521</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.551</v>
+        <v>-7.058068</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.601</v>
+        <v>-17.04773</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.585</v>
+        <v>-5.525788</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.053</v>
+        <v>-4.242618</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.29</v>
+        <v>-2.1685</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.505</v>
+        <v>-4.913558</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.988</v>
+        <v>-5.33651</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
@@ -1539,25 +1539,25 @@
         <v>-4.838869</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.253534</v>
+        <v>-3.253534</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8.223364999999999</v>
+        <v>-8.223364999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.470394</v>
+        <v>-2.470394</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.094809</v>
+        <v>-2.094809</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.22925</v>
+        <v>-1.22925</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.709279</v>
+        <v>-2.709279</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.162255</v>
+        <v>-3.162255</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
         <v>-4.838869</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.253534</v>
+        <v>-3.253534</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8.223364999999999</v>
+        <v>-8.223364999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.470394</v>
+        <v>-2.470394</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.094809</v>
+        <v>-2.094809</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.22925</v>
+        <v>-1.22925</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.709279</v>
+        <v>-2.709279</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.162255</v>
+        <v>-3.162255</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-7.893516</v>
@@ -1885,10 +1885,10 @@
         <v>161.295633</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>162.6767</v>
+        <v>-162.6767</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>164.4673</v>
+        <v>-164.4673</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2202,25 +2202,25 @@
         <v>-9.720386822886901</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>14.48271982849936</v>
+        <v>185.5172801715006</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6.810688361145532</v>
+        <v>193.1893116388545</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>19.14646687137567</v>
+        <v>180.8535331286243</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.46763096718563</v>
+        <v>197.5323690328144</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>30.8756986957679</v>
+        <v>230.8756986957679</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>22.90998553268438</v>
+        <v>222.9099855326844</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>45.44085215395619</v>
+        <v>245.4408521539562</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>50.53404674760277</v>
+        <v>-50.53404674760277</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>9.492844401473437</v>
+        <v>-9.492844401473437</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-882.1325551330478</v>
+        <v>882.1325551330478</v>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
@@ -6593,40 +6593,40 @@
         <v>-3.739273</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.82672</v>
+        <v>-0.22236</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.563927</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.272932</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-3.970223</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.228766</v>
+        <v>-2.367643</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.503916</v>
+        <v>-23.316239</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.052669</v>
+        <v>-32.714276</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.89317</v>
+        <v>-65.81467000000001</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>-0.396571</v>
+        <v>-63.63061</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.085879</v>
+        <v>-26.907645</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>4.377943</v>
+        <v>-14.079383</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>6.895346</v>
+        <v>-8.83127</v>
       </c>
     </row>
     <row r="119">
@@ -31778,7 +31778,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -49986,13 +49990,13 @@
         </is>
       </c>
       <c r="K506" s="5" t="n">
-        <v>1.22925</v>
+        <v>-1.22925</v>
       </c>
       <c r="L506" s="5" t="n">
-        <v>2.709279</v>
+        <v>-2.709279</v>
       </c>
       <c r="M506" s="5" t="n">
-        <v>3.162255</v>
+        <v>-3.162255</v>
       </c>
       <c r="N506" t="inlineStr">
         <is>
@@ -50156,13 +50160,13 @@
         </is>
       </c>
       <c r="K508" s="5" t="n">
-        <v>1.22925</v>
+        <v>-1.22925</v>
       </c>
       <c r="L508" s="5" t="n">
-        <v>3.093997</v>
+        <v>-3.093997</v>
       </c>
       <c r="M508" s="5" t="n">
-        <v>2.873717</v>
+        <v>-2.873717</v>
       </c>
       <c r="N508" t="inlineStr">
         <is>
@@ -51958,7 +51962,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr">
         <is>
           <t>-</t>
@@ -53588,10 +53596,10 @@
         </is>
       </c>
       <c r="I549" s="5" t="n">
-        <v>2.470394</v>
+        <v>-2.470394</v>
       </c>
       <c r="J549" s="5" t="n">
-        <v>2.094809</v>
+        <v>-2.094809</v>
       </c>
       <c r="K549" t="inlineStr">
         <is>
@@ -54208,7 +54216,11 @@
           <t>Royalty expense (note 16)</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -55502,13 +55514,13 @@
         <v>-4.838869</v>
       </c>
       <c r="G572" s="5" t="n">
-        <v>3.253534</v>
+        <v>-3.253534</v>
       </c>
       <c r="H572" s="5" t="n">
-        <v>8.223364999999999</v>
+        <v>-8.223364999999999</v>
       </c>
       <c r="I572" s="5" t="n">
-        <v>2.470394</v>
+        <v>-2.470394</v>
       </c>
       <c r="J572" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WM.xlsx
+++ b/output/pdf_financials_xlsx/WM.xlsx
@@ -1025,31 +1025,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012407</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.056779</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010468</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014804</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035485</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.062356</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.047447</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024961</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.2102</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1948,31 +1948,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.6702630000000001</v>
+        <v>-0.657856</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.359869</v>
+        <v>-5.30309</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.804534</v>
+        <v>3.815002</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8.824365</v>
+        <v>8.839169</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.055394</v>
+        <v>3.090879</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.147809</v>
+        <v>2.210165</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.93925</v>
+        <v>0.986697</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.204279</v>
+        <v>2.22924</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.174255</v>
+        <v>2.384455</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2066,31 +2066,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.6702630000000001</v>
+        <v>-0.657856</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.359869</v>
+        <v>-5.30309</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.804534</v>
+        <v>3.815002</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11.303065</v>
+        <v>11.317869</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.39429</v>
+        <v>6.429775</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.147809</v>
+        <v>2.210165</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.93925</v>
+        <v>0.986697</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.204279</v>
+        <v>2.22924</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.174255</v>
+        <v>2.384455</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>69.45935333056391</v>
+        <v>69.55032655479164</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>24.57097937733722</v>
+        <v>24.70733559565149</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-904.4510698148406</v>
+        <v>-930.7094339940455</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -6904,25 +6904,25 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.053223</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.7058449999999999</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.136898</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.094801</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015845</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014906</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010185</v>
       </c>
     </row>
     <row r="125">
@@ -6953,25 +6953,25 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.053223</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.7058449999999999</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.136898</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.094801</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015845</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014906</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010185</v>
       </c>
     </row>
     <row r="126">
@@ -31640,7 +31640,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -48704,7 +48708,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -58972,7 +58976,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E613" s="5" t="n">

--- a/output/pdf_financials_xlsx/WM.xlsx
+++ b/output/pdf_financials_xlsx/WM.xlsx
@@ -5732,19 +5732,19 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.17364</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.129196</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.047858</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.031802</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.033425</v>
       </c>
     </row>
     <row r="101">
@@ -6293,19 +6293,19 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.02209</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.210589</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.002228</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -30204,7 +30204,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -42084,7 +42088,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E413" s="5" t="n">
         <v>0.02209</v>
       </c>

--- a/output/pdf_financials_xlsx/WM.xlsx
+++ b/output/pdf_financials_xlsx/WM.xlsx
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.19497</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.141381</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.2747</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -6277,13 +6277,13 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.235721</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.274267</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.664548</v>
       </c>
     </row>
     <row r="112">
@@ -6458,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.041529</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -6467,19 +6467,19 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.215127</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.031451</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.865861</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.498418</v>
       </c>
     </row>
     <row r="116">
@@ -7434,13 +7434,13 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.235721</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.274267</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.664548</v>
       </c>
     </row>
     <row r="135">
@@ -7483,10 +7483,10 @@
         <v>-4.401313</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-3.768597</v>
+        <v>-4.004318</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-4.55139</v>
+        <v>-4.825657</v>
       </c>
       <c r="O135" s="1" t="inlineStr">
         <is>
@@ -30136,7 +30136,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>0.38</v>
       </c>
@@ -32190,7 +32194,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -32448,7 +32456,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -34182,7 +34194,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -34348,7 +34364,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -39548,7 +39568,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -40062,7 +40086,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -57558,7 +57586,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E596" s="5" t="n">
         <v>0.19497</v>
       </c>
